--- a/code.xlsx
+++ b/code.xlsx
@@ -22390,8 +22390,10 @@
       <c r="A335" t="s">
         <v>995</v>
       </c>
-      <c r="B335" t="s">
-        <v>996</v>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>宏碁</t>
+        </is>
       </c>
       <c r="C335" t="s">
         <v>7</v>
@@ -23359,8 +23361,10 @@
       <c r="A392" t="s">
         <v>1148</v>
       </c>
-      <c r="B392" t="s">
-        <v>1149</v>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>倚天酷碁-創</t>
+        </is>
       </c>
       <c r="C392" t="s">
         <v>899</v>
@@ -27201,8 +27205,10 @@
       <c r="A618" t="s">
         <v>1748</v>
       </c>
-      <c r="B618" t="s">
-        <v>1749</v>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>建碁</t>
+        </is>
       </c>
       <c r="C618" t="s">
         <v>7</v>
@@ -39084,8 +39090,10 @@
       <c r="A1317" t="s">
         <v>3681</v>
       </c>
-      <c r="B1317" t="s">
-        <v>3682</v>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>安碁</t>
+        </is>
       </c>
       <c r="C1317" t="s">
         <v>86</v>
@@ -40580,8 +40588,10 @@
       <c r="A1405" t="s">
         <v>3903</v>
       </c>
-      <c r="B1405" t="s">
-        <v>3904</v>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
       </c>
       <c r="C1405" t="s">
         <v>7</v>
@@ -43028,8 +43038,10 @@
       <c r="A1549" t="s">
         <v>4301</v>
       </c>
-      <c r="B1549" t="s">
-        <v>4302</v>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>安碁資訊</t>
+        </is>
       </c>
       <c r="C1549" t="s">
         <v>86</v>
@@ -43725,8 +43737,10 @@
       <c r="A1590" t="s">
         <v>4421</v>
       </c>
-      <c r="B1590" t="s">
-        <v>4422</v>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
       </c>
       <c r="C1590" t="s">
         <v>7</v>
@@ -43997,8 +44011,10 @@
       <c r="A1606" t="s">
         <v>4467</v>
       </c>
-      <c r="B1606" t="s">
-        <v>4468</v>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>宏碁資訊</t>
+        </is>
       </c>
       <c r="C1606" t="s">
         <v>86</v>
@@ -44728,8 +44744,10 @@
       <c r="A1649" t="s">
         <v>4586</v>
       </c>
-      <c r="B1649" t="s">
-        <v>4587</v>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>宏碁遊戲-創</t>
+        </is>
       </c>
       <c r="C1649" t="s">
         <v>899</v>
@@ -46343,8 +46361,10 @@
       <c r="A1744" t="s">
         <v>4839</v>
       </c>
-      <c r="B1744" t="s">
-        <v>4840</v>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>宏碁智新</t>
+        </is>
       </c>
       <c r="C1744" t="s">
         <v>86</v>
@@ -47193,8 +47213,10 @@
       <c r="A1794" t="s">
         <v>4967</v>
       </c>
-      <c r="B1794" t="s">
-        <v>4968</v>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>洛碁</t>
+        </is>
       </c>
       <c r="C1794" t="s">
         <v>86</v>
@@ -48196,8 +48218,10 @@
       <c r="A1853" t="s">
         <v>5118</v>
       </c>
-      <c r="B1853" t="s">
-        <v>5119</v>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>恒耀</t>
+        </is>
       </c>
       <c r="C1853" t="s">
         <v>86</v>
